--- a/reports/pdf_rolling5_20260825.xlsx
+++ b/reports/pdf_rolling5_20260825.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,7 +171,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-18 ~ 2026-08-25  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-18 ~ 2026-08-25  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 86억(1.9%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 13종목  /  매도 20종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 65억(1.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 22종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -662,19 +667,19 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>11971386000</v>
+        <v>11866016400</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.75%</t>
+          <t>0.00%→2.69%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>0→420</t>
+          <t>0→454</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -686,7 +691,7 @@
         <v>-283</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2722785450</v>
+        <v>-2751906150</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,11 +714,11 @@
         <v>196</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9055611600</v>
+        <v>8864011800</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.08%</t>
+          <t>0.00%→2.01%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -730,11 +735,11 @@
         <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1231558650</v>
+        <v>-1199340660</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.43%</t>
+          <t>0.77%→0.41%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -753,7 +758,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>443596755</v>
+        <v>447085065</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,11 +779,11 @@
         <v>-93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1232577360</v>
+        <v>-1275641010</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.52%</t>
+          <t>0.94%→0.53%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -794,19 +799,19 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1378036800</v>
+        <v>2358931050</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.62%</t>
+          <t>1.27%→1.90%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>222→276</t>
+          <t>222→309</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -818,11 +823,11 @@
         <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2845185000</v>
+        <v>-2804539500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>1.63%→0.98%</t>
+          <t>1.63%→0.96%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -834,23 +839,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>하림지주</t>
+          <t>아이티센글로벌  (신규)</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>468133260</v>
+        <v>2300946900</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.61%→0.72%</t>
+          <t>0.00%→0.52%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>244→287</t>
+          <t>0→59</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -862,11 +867,11 @@
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1272770100</v>
+        <v>-1415492400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.28%</t>
+          <t>0.64%→0.30%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
@@ -878,380 +883,396 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>하림지주</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>415633680</v>
+        <v>484062180</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.02%</t>
+          <t>0.61%→0.73%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>349→385</t>
+          <t>244→287</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1757737800</v>
+        <v>-2627448600</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>6.32%→5.77%</t>
+          <t>0.77%→0.12%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>398→372</t>
+          <t>41→7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>844037250</v>
+        <v>417115440</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.52%</t>
+          <t>1.05%→1.01%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>116→133</t>
+          <t>349→385</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-895230000</v>
+        <v>-2127148800</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.63%</t>
+          <t>6.32%→5.51%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>98→74</t>
+          <t>398→366</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1474042500</v>
+        <v>857157000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.93%→1.13%</t>
+          <t>1.43%→1.52%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>116→133</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스  (편출)</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-428846040</v>
+        <v>-759196200</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>3.60%→3.27%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>787→764</t>
+          <t>31→0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>434340900</v>
+        <v>1450890000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.40%</t>
+          <t>0.93%→1.09%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>42→56</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>태웅</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-405528900</v>
+        <v>-942152400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.78%</t>
+          <t>0.81%→0.66%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>132→118</t>
+          <t>98→74</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>503798400</v>
+        <v>450907800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.14%</t>
+          <t>0.33%→0.41%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>106→118</t>
+          <t>42→56</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-12</v>
+        <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-441441000</v>
+        <v>-424585980</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.36%</t>
+          <t>3.60%→3.19%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>787→764</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>870431100</v>
+        <v>518616000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.77%→0.94%</t>
+          <t>0.89%→1.15%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>41→52</t>
+          <t>106→118</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-12</v>
+        <v>-22</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-272273400</v>
+        <v>-1715960400</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.10%</t>
+          <t>1.98%→1.47%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>105→83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>923321700</v>
+        <v>3297945000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.19%→1.39%</t>
+          <t>6.13%→7.24%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>50→59</t>
+          <t>87→97</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>태웅</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-207590460</v>
+        <v>-403368000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.23%</t>
+          <t>1.04%→0.77%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>64→53</t>
+          <t>132→118</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2304960000</v>
+        <v>2106877500</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>6.13%→7.11%</t>
+          <t>0.00%→0.48%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>87→94</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-851188800</v>
+        <v>-433414800</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.98%→1.67%</t>
+          <t>1.48%→1.32%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>105→94</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>1020562200</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>1.19%→1.51%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>50→59</t>
+        </is>
+      </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-312404400</v>
+        <v>-1299009600</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.51%</t>
+          <t>4.49%→4.21%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1263,23 +1284,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-880206600</v>
+        <v>-204307950</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.29%→1.99%</t>
+          <t>0.31%→0.22%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>64→53</t>
         </is>
       </c>
     </row>
@@ -1291,23 +1312,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-820524600</v>
+        <v>-367147200</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.65%→6.12%</t>
+          <t>0.58%→0.59%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>201→195</t>
+          <t>65→57</t>
         </is>
       </c>
     </row>
@@ -1319,23 +1340,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1306830000</v>
+        <v>-902535900</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>3.45%→3.00%</t>
+          <t>2.29%→2.01%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1347,23 +1368,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-426520500</v>
+        <v>-196281750</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.51%</t>
+          <t>0.60%→0.48%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1375,23 +1396,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-410365200</v>
+        <v>-823611600</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>4.49%→4.24%</t>
+          <t>6.65%→6.06%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>184→180</t>
+          <t>201→195</t>
         </is>
       </c>
     </row>
@@ -1403,367 +1424,367 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-1273387500</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>3.45%→2.88%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>55→50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-450702000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>0.66%→0.53%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>31→26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H27" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I25" s="15" t="n">
-        <v>-411600000</v>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>1.76%→1.54%</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="I27" s="15" t="n">
+        <v>-423536400</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>1.76%→1.56%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>69→65</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 39억(1.0%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>564</v>
-      </c>
-      <c r="C30" s="11" t="n">
-        <v>4678391280</v>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.27%</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>0→564</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>나이벡  (편출)</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>-527</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>-4712434000</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>1.18%→0.00%</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>527→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>에이프릴바이오</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>720072960</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>3.73%→3.02%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>999→1,068</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-155</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-1703977000</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>1.09%→0.57%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>345→190</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
-        <v>50</v>
+        <v>564</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>724565000</v>
+        <v>4494459600</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.60%</t>
+          <t>0.00%→1.16%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>613→663</t>
+          <t>0→564</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>나이벡  (편출)</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-6</v>
+        <v>-527</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1009920000</v>
+        <v>-4712434000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>9.37%→10.04%</t>
+          <t>1.18%→0.00%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>226→220</t>
+          <t>527→0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>713256000</v>
+        <v>723702360</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>5.20%→5.50%</t>
+          <t>3.73%→2.89%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>659→683</t>
+          <t>999→1,068</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-5</v>
+        <v>-155</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-321123000</v>
+        <v>-1716206500</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>3.12%→3.10%</t>
+          <t>1.09%→0.54%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>183→178</t>
+          <t>345→190</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>711993600</v>
+        <v>792945000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>8.85%→8.74%</t>
+          <t>2.62%→2.71%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>797→815</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="17" t="n"/>
-      <c r="J34" s="17" t="n"/>
-      <c r="K34" s="17" t="n"/>
+          <t>613→663</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-1011498000</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>9.37%→9.56%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>226→220</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>670807800</v>
+        <v>754915200</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>7.99%→7.74%</t>
+          <t>5.20%→5.54%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>540→553</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="n"/>
-      <c r="H35" s="17" t="n"/>
-      <c r="I35" s="17" t="n"/>
-      <c r="J35" s="17" t="n"/>
-      <c r="K35" s="17" t="n"/>
+          <t>659→683</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-342689000</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>3.12%→3.14%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>183→178</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>631989000</v>
+        <v>717674400</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>4.73%→5.31%</t>
+          <t>8.85%→8.37%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>90→93</t>
+          <t>797→815</t>
         </is>
       </c>
       <c r="G36" s="17" t="n"/>
@@ -1772,862 +1793,1344 @@
       <c r="J36" s="17" t="n"/>
       <c r="K36" s="17" t="n"/>
     </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="19" t="n"/>
-      <c r="F38" s="19" t="n"/>
-      <c r="G38" s="19" t="n"/>
-      <c r="H38" s="19" t="n"/>
-      <c r="I38" s="19" t="n"/>
-      <c r="J38" s="19" t="n"/>
-      <c r="K38" s="19" t="n"/>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>698843600</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>7.99%→7.66%</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>540→553</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>656448000</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>4.73%→5.24%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>90→93</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="n"/>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="17" t="n"/>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-      <c r="E40" s="19" t="n"/>
-      <c r="F40" s="19" t="n"/>
-      <c r="G40" s="19" t="n"/>
-      <c r="H40" s="19" t="n"/>
-      <c r="I40" s="19" t="n"/>
-      <c r="J40" s="19" t="n"/>
-      <c r="K40" s="19" t="n"/>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 12종목  /  매도 6종목</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억   ·   현금 74억(2.9%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억   ·   현금 56억(2.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 10종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>코미코  (신규)</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>395</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>809671000</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→3.03%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>0→395</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-71</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-190457500</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>8.23%→7.27%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>795→724</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>65413040</v>
+        <v>5949801000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.16%→0.40%</t>
+          <t>1.75%→4.51%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>51→133</t>
+          <t>200→497</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-34</v>
+        <v>-222</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-23524600</v>
+        <v>-1482937800</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.50%</t>
+          <t>1.97%→0.77%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>227→193</t>
+          <t>475→253</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>69</v>
+        <v>188</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>41154360</v>
+        <v>4566050000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.28%→0.43%</t>
+          <t>1.51%→3.73%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>122→191</t>
+          <t>151→339</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>고영  (편출)</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-24</v>
+        <v>-194</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-84626400</v>
+        <v>-2102426500</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.70%</t>
+          <t>0.92%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>77→53</t>
+          <t>194→0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>30800280</v>
+        <v>4354330000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.42%</t>
+          <t>13.34%→15.31%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>474→516</t>
+          <t>453→520</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-16</v>
+        <v>-184</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-53161600</v>
+        <v>-6792728000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.31%</t>
+          <t>3.90%→1.10%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>121→105</t>
+          <t>250→66</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>64135800</v>
+        <v>3144176000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.94%→3.09%</t>
+          <t>2.63%→3.97%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>321→348</t>
+          <t>100→156</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
-        <v>-11</v>
+        <v>-125</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-43386200</v>
+        <v>-4308937500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.28%</t>
+          <t>6.49%→4.12%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>389→264</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱  (신규)</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>100936000</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.38%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>0→22</t>
-        </is>
-      </c>
+      <c r="A50" s="17" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-3</v>
+        <v>-102</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-34254600</v>
+        <v>-2115123000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.81%→1.62%</t>
+          <t>0.92%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>41→38</t>
+          <t>102→0</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>20631200</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>3.18%→3.17%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>680→697</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="n"/>
-      <c r="H51" s="17" t="n"/>
-      <c r="I51" s="17" t="n"/>
-      <c r="J51" s="17" t="n"/>
-      <c r="K51" s="17" t="n"/>
+      <c r="A51" s="17" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-886711500</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.40%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>203→101</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>24745600</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>5.83%→5.75%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>977→993</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="n"/>
-      <c r="H52" s="17" t="n"/>
-      <c r="I52" s="17" t="n"/>
-      <c r="J52" s="17" t="n"/>
-      <c r="K52" s="17" t="n"/>
+      <c r="A52" s="17" t="n"/>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-221421600</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.15%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>199→118</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>20823600</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>2.38%→2.38%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>355→367</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="17" t="n"/>
-      <c r="J53" s="17" t="n"/>
-      <c r="K53" s="17" t="n"/>
+      <c r="A53" s="17" t="n"/>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-68</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-686817000</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>0.71%→0.38%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>150→82</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>22977000</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>2.73%→2.74%</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>154→159</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="n"/>
-      <c r="H54" s="17" t="n"/>
-      <c r="I54" s="17" t="n"/>
-      <c r="J54" s="17" t="n"/>
-      <c r="K54" s="17" t="n"/>
+      <c r="A54" s="17" t="n"/>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>토모큐브</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-446387500</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>0.54%→0.30%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>101→60</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>39775000</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>3.13%→3.19%</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>102→107</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="n"/>
-      <c r="H55" s="17" t="n"/>
-      <c r="I55" s="17" t="n"/>
-      <c r="J55" s="17" t="n"/>
-      <c r="K55" s="17" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>보로노이  (신규)</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="11" t="n">
-        <v>22510800</v>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.08%</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>0→2</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="n"/>
-      <c r="H56" s="17" t="n"/>
-      <c r="I56" s="17" t="n"/>
-      <c r="J56" s="17" t="n"/>
-      <c r="K56" s="17" t="n"/>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 6억(1.1%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
+      <c r="A55" s="17" t="n"/>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-229274000</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.16%→0.06%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>46→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 12종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>코미코  (신규)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>395</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>809671000</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.03%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>0→395</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-71</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-190457500</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>8.23%→7.27%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>795→724</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
-        <v>878</v>
+        <v>82</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>1619989020</v>
+        <v>65413040</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.07%</t>
+          <t>0.16%→0.40%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>0→878</t>
+          <t>51→133</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-301</v>
+        <v>-34</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-599041170</v>
+        <v>-23524600</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.66%→1.17%</t>
+          <t>0.61%→0.50%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>612→311</t>
+          <t>227→193</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>프로티나  (신규)</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
-        <v>227</v>
+        <v>69</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>974715300</v>
+        <v>41154360</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.85%</t>
+          <t>0.28%→0.43%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>0→227</t>
+          <t>122→191</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-230</v>
+        <v>-24</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-533894400</v>
+        <v>-84626400</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.71%→1.03%</t>
+          <t>1.05%→0.70%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>464→234</t>
+          <t>77→53</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>261038700</v>
+        <v>30800280</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>3.63%→3.83%</t>
+          <t>1.34%→1.42%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>498→572</t>
+          <t>474→516</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>리브스메드</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-116</v>
+        <v>-16</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-453983400</v>
+        <v>-53161600</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>3.31%→1.73%</t>
+          <t>1.55%→1.31%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>349→233</t>
+          <t>121→105</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>64135800</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>2.94%→3.09%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>321→348</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-43386200</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>0.46%→0.28%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>30→19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>100936000</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.38%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-34254600</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>1.81%→1.62%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>20631200</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>3.18%→3.17%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>680→697</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="17" t="n"/>
+      <c r="I66" s="17" t="n"/>
+      <c r="J66" s="17" t="n"/>
+      <c r="K66" s="17" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>24745600</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>5.83%→5.75%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>977→993</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="n"/>
+      <c r="H67" s="17" t="n"/>
+      <c r="I67" s="17" t="n"/>
+      <c r="J67" s="17" t="n"/>
+      <c r="K67" s="17" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>20823600</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>2.38%→2.38%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>355→367</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="n"/>
+      <c r="H68" s="17" t="n"/>
+      <c r="I68" s="17" t="n"/>
+      <c r="J68" s="17" t="n"/>
+      <c r="K68" s="17" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>22977000</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>2.73%→2.74%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>154→159</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="n"/>
+      <c r="H69" s="17" t="n"/>
+      <c r="I69" s="17" t="n"/>
+      <c r="J69" s="17" t="n"/>
+      <c r="K69" s="17" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>39775000</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>3.13%→3.19%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G70" s="17" t="n"/>
+      <c r="H70" s="17" t="n"/>
+      <c r="I70" s="17" t="n"/>
+      <c r="J70" s="17" t="n"/>
+      <c r="K70" s="17" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>보로노이  (신규)</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>22510800</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.08%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>0→2</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="n"/>
+      <c r="H71" s="17" t="n"/>
+      <c r="I71" s="17" t="n"/>
+      <c r="J71" s="17" t="n"/>
+      <c r="K71" s="17" t="n"/>
+    </row>
+    <row r="73" ht="19" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="8" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>878</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>1556298900</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.79%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>0→878</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>한스바이오메드</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-301</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>-649753650</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>2.66%→1.20%</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>612→311</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>227</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>912301650</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.64%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>0→227</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>-536585400</v>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>2.71%→0.98%</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>464→234</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>270995400</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>3.63%→3.76%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>498→572</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I78" s="15" t="n">
+        <v>-475698600</v>
+      </c>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>3.31%→1.71%</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>349→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
           <t>에스티팜</t>
         </is>
       </c>
-      <c r="B64" s="11" t="n">
+      <c r="B79" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C64" s="11" t="n">
-        <v>256627800</v>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>5.63%→6.15%</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="C79" s="11" t="n">
+        <v>283654800</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>5.63%→6.43%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>256→278</t>
         </is>
       </c>
-      <c r="G64" s="14" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>휴젤</t>
         </is>
       </c>
-      <c r="H64" s="15" t="n">
+      <c r="H79" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I64" s="15" t="n">
-        <v>-573300000</v>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>3.54%→2.56%</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="I79" s="15" t="n">
+        <v>-586170000</v>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>3.54%→2.47%</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
         <is>
           <t>67→47</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="18" t="inlineStr">
+    <row r="81" ht="19" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B66" s="19" t="n"/>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
-      <c r="G66" s="19" t="n"/>
-      <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
-      <c r="J66" s="19" t="n"/>
-      <c r="K66" s="19" t="n"/>
+      <c r="B81" s="20" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="20" t="n"/>
+      <c r="E81" s="20" t="n"/>
+      <c r="F81" s="20" t="n"/>
+      <c r="G81" s="20" t="n"/>
+      <c r="H81" s="20" t="n"/>
+      <c r="I81" s="20" t="n"/>
+      <c r="J81" s="20" t="n"/>
+      <c r="K81" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A58:K58"/>
+  <mergeCells count="20">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="G74:K74"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="G58:K58"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="G43:K43"/>
-    <mergeCell ref="G59:K59"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G28:K28"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A66:K66"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260825.xlsx
+++ b/reports/pdf_rolling5_20260825.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 65억(1.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 22종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 33억(0.7%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 22종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-433414800</v>
+        <v>-1299009600</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.32%</t>
+          <t>4.49%→4.21%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1256,23 +1256,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1299009600</v>
+        <v>-433414800</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>4.49%→4.21%</t>
+          <t>1.48%→1.32%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1340,23 +1340,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-902535900</v>
+        <v>-196281750</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.01%</t>
+          <t>0.60%→0.48%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1368,23 +1368,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-196281750</v>
+        <v>-902535900</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.48%</t>
+          <t>2.29%→2.01%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 39억(1.0%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 19억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1852,7 +1852,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억   ·   현금 74억(2.9%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억   ·   현금 37억(1.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1876,7 +1876,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억   ·   현금 56억(2.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억   ·   현금 28억(1.2%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -2146,23 +2146,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>에임드바이오</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-2115123000</v>
+        <v>-886711500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.00%</t>
+          <t>0.81%→0.40%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>102→0</t>
+          <t>203→101</t>
         </is>
       </c>
     </row>
@@ -2174,23 +2174,23 @@
       <c r="E51" s="17" t="n"/>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>에임드바이오</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-886711500</v>
+        <v>-2115123000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.40%</t>
+          <t>0.92%→0.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>203→101</t>
+          <t>102→0</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 12종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 3억(1.0%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2402,19 +2402,19 @@
         </is>
       </c>
       <c r="B60" s="11" t="n">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>809671000</v>
+        <v>731778600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.03%</t>
+          <t>0.00%→2.75%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>0→395</t>
+          <t>0→357</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>8.23%→7.27%</t>
+          <t>8.23%→7.29%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2442,250 +2442,266 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>65413040</v>
+        <v>117719200</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.16%→0.40%</t>
+          <t>3.18%→3.54%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>51→133</t>
+          <t>680→777</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-34</v>
+        <v>-71</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-23524600</v>
+        <v>-45184400</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.50%</t>
+          <t>7.49%→7.12%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>227→193</t>
+          <t>3,052→2,981</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>41154360</v>
+        <v>65413040</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.28%→0.43%</t>
+          <t>0.16%→0.40%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>122→191</t>
+          <t>51→133</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-24</v>
+        <v>-35</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-84626400</v>
+        <v>-84304500</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.70%</t>
+          <t>3.11%→2.71%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>77→53</t>
+          <t>335→300</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>코스맥스엔비티</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>30800280</v>
+        <v>41154360</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.42%</t>
+          <t>0.28%→0.43%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>474→516</t>
+          <t>122→191</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-16</v>
+        <v>-34</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-53161600</v>
+        <v>-23524600</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.31%</t>
+          <t>0.61%→0.50%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>121→105</t>
+          <t>227→193</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>64135800</v>
+        <v>30800280</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.94%→3.09%</t>
+          <t>1.34%→1.42%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>321→348</t>
+          <t>474→516</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
-        <v>-11</v>
+        <v>-31</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-43386200</v>
+        <v>-25142240</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.28%</t>
+          <t>2.84%→2.67%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>907→876</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>오름테라퓨틱  (신규)</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>100936000</v>
+        <v>64135800</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.38%</t>
+          <t>2.94%→3.10%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>0→22</t>
+          <t>321→348</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H65" s="15" t="n">
-        <v>-3</v>
+        <v>-24</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-34254600</v>
+        <v>-84626400</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.81%→1.62%</t>
+          <t>1.05%→0.70%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
-          <t>41→38</t>
+          <t>77→53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>오름테라퓨틱  (신규)</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>20631200</v>
+        <v>100936000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>3.18%→3.17%</t>
+          <t>0.00%→0.38%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>680→697</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="n"/>
-      <c r="H66" s="17" t="n"/>
-      <c r="I66" s="17" t="n"/>
-      <c r="J66" s="17" t="n"/>
-      <c r="K66" s="17" t="n"/>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-67051400</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>0.46%→0.19%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>30→13</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -2701,7 +2717,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>5.83%→5.75%</t>
+          <t>5.83%→5.76%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2709,60 +2725,92 @@
           <t>977→993</t>
         </is>
       </c>
-      <c r="G67" s="17" t="n"/>
-      <c r="H67" s="17" t="n"/>
-      <c r="I67" s="17" t="n"/>
-      <c r="J67" s="17" t="n"/>
-      <c r="K67" s="17" t="n"/>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-53161600</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>1.55%→1.31%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>121→105</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>20823600</v>
+        <v>42328000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.38%</t>
+          <t>1.06%→1.19%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>355→367</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="n"/>
-      <c r="H68" s="17" t="n"/>
-      <c r="I68" s="17" t="n"/>
-      <c r="J68" s="17" t="n"/>
-      <c r="K68" s="17" t="n"/>
+          <t>104→120</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-34254600</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>1.81%→1.63%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>22977000</v>
+        <v>20823600</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>2.73%→2.74%</t>
+          <t>2.38%→2.39%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>154→159</t>
+          <t>355→367</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -2774,23 +2822,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>39775000</v>
+        <v>54545400</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.19%</t>
+          <t>1.05%→1.23%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>35→42</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>
@@ -2802,23 +2850,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>보로노이  (신규)</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>22510800</v>
+        <v>22977000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.08%</t>
+          <t>2.73%→2.74%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>0→2</t>
+          <t>154→159</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
@@ -2827,306 +2875,362 @@
       <c r="J71" s="17" t="n"/>
       <c r="K71" s="17" t="n"/>
     </row>
-    <row r="73" ht="19" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>39775000</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>3.13%→3.19%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="n"/>
+      <c r="H72" s="17" t="n"/>
+      <c r="I72" s="17" t="n"/>
+      <c r="J72" s="17" t="n"/>
+      <c r="K72" s="17" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>보로노이  (신규)</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>22510800</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.08%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>0→2</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="n"/>
+      <c r="H73" s="17" t="n"/>
+      <c r="I73" s="17" t="n"/>
+      <c r="J73" s="17" t="n"/>
+      <c r="K73" s="17" t="n"/>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="8" t="n"/>
-      <c r="J74" s="8" t="n"/>
-      <c r="K74" s="8" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr">
+      <c r="H77" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K77" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="n">
-        <v>878</v>
-      </c>
-      <c r="C76" s="11" t="n">
-        <v>1556298900</v>
-      </c>
-      <c r="D76" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→2.79%</t>
-        </is>
-      </c>
-      <c r="E76" s="13" t="inlineStr">
-        <is>
-          <t>0→878</t>
-        </is>
-      </c>
-      <c r="G76" s="14" t="inlineStr">
-        <is>
-          <t>한스바이오메드</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>-301</v>
-      </c>
-      <c r="I76" s="15" t="n">
-        <v>-649753650</v>
-      </c>
-      <c r="J76" s="16" t="inlineStr">
-        <is>
-          <t>2.66%→1.20%</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>612→311</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>프로티나  (신규)</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="n">
-        <v>227</v>
-      </c>
-      <c r="C77" s="11" t="n">
-        <v>912301650</v>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.64%</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>0→227</t>
-        </is>
-      </c>
-      <c r="G77" s="14" t="inlineStr">
-        <is>
-          <t>에이프릴바이오</t>
-        </is>
-      </c>
-      <c r="H77" s="15" t="n">
-        <v>-230</v>
-      </c>
-      <c r="I77" s="15" t="n">
-        <v>-536585400</v>
-      </c>
-      <c r="J77" s="16" t="inlineStr">
-        <is>
-          <t>2.71%→0.98%</t>
-        </is>
-      </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>464→234</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
-        <v>74</v>
+        <v>878</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>270995400</v>
+        <v>1556298900</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>3.63%→3.76%</t>
+          <t>0.00%→2.79%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>498→572</t>
+          <t>0→878</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>리브스메드</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-116</v>
+        <v>-301</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-475698600</v>
+        <v>-649753650</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>3.31%→1.71%</t>
+          <t>2.66%→1.20%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
         <is>
-          <t>349→233</t>
+          <t>612→311</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>227</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>912301650</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.64%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>0→227</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>-536585400</v>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>2.71%→0.98%</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>464→234</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>270995400</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>3.63%→3.76%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>498→572</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <v>-475698600</v>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>3.31%→1.71%</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>349→233</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
           <t>에스티팜</t>
         </is>
       </c>
-      <c r="B79" s="11" t="n">
+      <c r="B81" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C79" s="11" t="n">
+      <c r="C81" s="11" t="n">
         <v>283654800</v>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>5.63%→6.43%</t>
         </is>
       </c>
-      <c r="E79" s="13" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>256→278</t>
         </is>
       </c>
-      <c r="G79" s="14" t="inlineStr">
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>휴젤</t>
         </is>
       </c>
-      <c r="H79" s="15" t="n">
+      <c r="H81" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I79" s="15" t="n">
+      <c r="I81" s="15" t="n">
         <v>-586170000</v>
       </c>
-      <c r="J79" s="16" t="inlineStr">
+      <c r="J81" s="16" t="inlineStr">
         <is>
           <t>3.54%→2.47%</t>
         </is>
       </c>
-      <c r="K79" s="13" t="inlineStr">
+      <c r="K81" s="13" t="inlineStr">
         <is>
           <t>67→47</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="19" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B81" s="20" t="n"/>
-      <c r="C81" s="20" t="n"/>
-      <c r="D81" s="20" t="n"/>
-      <c r="E81" s="20" t="n"/>
-      <c r="F81" s="20" t="n"/>
-      <c r="G81" s="20" t="n"/>
-      <c r="H81" s="20" t="n"/>
-      <c r="I81" s="20" t="n"/>
-      <c r="J81" s="20" t="n"/>
-      <c r="K81" s="20" t="n"/>
+      <c r="B83" s="20" t="n"/>
+      <c r="C83" s="20" t="n"/>
+      <c r="D83" s="20" t="n"/>
+      <c r="E83" s="20" t="n"/>
+      <c r="F83" s="20" t="n"/>
+      <c r="G83" s="20" t="n"/>
+      <c r="H83" s="20" t="n"/>
+      <c r="I83" s="20" t="n"/>
+      <c r="J83" s="20" t="n"/>
+      <c r="K83" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A83:K83"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="G74:K74"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="G30:K30"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A57:K57"/>
     <mergeCell ref="G58:K58"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G76:K76"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A81:K81"/>
     <mergeCell ref="G44:K44"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A58:E58"/>

--- a/reports/pdf_rolling5_20260825.xlsx
+++ b/reports/pdf_rolling5_20260825.xlsx
@@ -2309,7 +2309,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 3억(1.0%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2419,23 +2419,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-71</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-190457500</v>
+        <v>-45184400</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>8.23%→7.29%</t>
+          <t>7.49%→7.12%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>795→724</t>
+          <t>3,052→2,981</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-71</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-45184400</v>
+        <v>-190457500</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>7.49%→7.12%</t>
+          <t>8.23%→7.29%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>3,052→2,981</t>
+          <t>795→724</t>
         </is>
       </c>
     </row>
@@ -2706,23 +2706,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>24745600</v>
+        <v>42328000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>5.83%→5.76%</t>
+          <t>1.06%→1.19%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>977→993</t>
+          <t>104→120</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2750,23 +2750,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>42328000</v>
+        <v>24745600</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.19%</t>
+          <t>5.83%→5.76%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>104→120</t>
+          <t>977→993</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -2850,23 +2850,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>22977000</v>
+        <v>39775000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.73%→2.74%</t>
+          <t>3.13%→3.19%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>154→159</t>
+          <t>102→107</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
@@ -2878,23 +2878,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>39775000</v>
+        <v>22977000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.19%</t>
+          <t>2.73%→2.74%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>154→159</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260825.xlsx
+++ b/reports/pdf_rolling5_20260825.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,403억   ·   현금 33억(0.7%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 22종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 33억(0.7%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 22종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>454</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>11866016400</v>
+        <v>11877548000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-283</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2751906150</v>
+        <v>-2754580500</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>196</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8864011800</v>
+        <v>8872626000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1199340660</v>
+        <v>-1200506200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>447085065</v>
+        <v>447519550</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1275641010</v>
+        <v>-1276880700</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>87</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2358931050</v>
+        <v>2361223500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2804539500</v>
+        <v>-2807265000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>59</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2300946900</v>
+        <v>2303183000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-38</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1415492400</v>
+        <v>-1416868000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>484062180</v>
+        <v>484532600</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-34</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2627448600</v>
+        <v>-2630002000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>36</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>417115440</v>
+        <v>417520800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-32</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2127148800</v>
+        <v>-2129216000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>857157000</v>
+        <v>857990000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-31</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-759196200</v>
+        <v>-759934000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1450890000</v>
+        <v>1452300000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-24</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-942152400</v>
+        <v>-943068000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>450907800</v>
+        <v>451346000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-23</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-424585980</v>
+        <v>-424998600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>518616000</v>
+        <v>519120000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-22</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1715960400</v>
+        <v>-1717628000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3297945000</v>
+        <v>3301150000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-403368000</v>
+        <v>-403760000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>9</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2106877500</v>
+        <v>2108925000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1299009600</v>
+        <v>-1300272000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1020562200</v>
+        <v>1021554000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-12</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-433414800</v>
+        <v>-433836000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>-11</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-204307950</v>
+        <v>-204506500</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-367147200</v>
+        <v>-367504000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1340,23 +1340,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-196281750</v>
+        <v>-903413000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.48%</t>
+          <t>2.29%→2.01%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1368,23 +1368,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-902535900</v>
+        <v>-196472500</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.01%</t>
+          <t>0.60%→0.48%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-823611600</v>
+        <v>-824412000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1424,23 +1424,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1273387500</v>
+        <v>-451140000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>3.45%→2.88%</t>
+          <t>0.66%→0.53%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -1452,23 +1452,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-450702000</v>
+        <v>-1274625000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.53%</t>
+          <t>3.45%→2.88%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
         <v>-4</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-423536400</v>
+        <v>-423948000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 19억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 19억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1599,7 +1599,7 @@
         <v>564</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>4494459600</v>
+        <v>4485915000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>-527</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-4712434000</v>
+        <v>-4703475000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>69</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>723702360</v>
+        <v>722326500</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>-155</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1716206500</v>
+        <v>-1712943750</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>50</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>792945000</v>
+        <v>791437500</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>-6</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1011498000</v>
+        <v>-1009575000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>754915200</v>
+        <v>753480000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>-5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-342689000</v>
+        <v>-342037500</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>18</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>717674400</v>
+        <v>716310000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>13</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>698843600</v>
+        <v>697515000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>656448000</v>
+        <v>655200000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,499억   ·   현금 37억(1.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 37억(1.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1876,7 +1876,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,149억   ·   현금 28억(1.2%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억   ·   현금 28억(1.2%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1972,7 +1972,7 @@
         <v>297</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>5949801000</v>
+        <v>5985322200</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>-222</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1482937800</v>
+        <v>-1491791160</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>188</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>4566050000</v>
+        <v>4593310000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>-194</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-2102426500</v>
+        <v>-2114978300</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>67</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4354330000</v>
+        <v>4380326000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>-184</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-6792728000</v>
+        <v>-6833281600</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>3144176000</v>
+        <v>3162947200</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>-125</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-4308937500</v>
+        <v>-4334662500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>-102</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-886711500</v>
+        <v>-892005300</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>-102</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-2115123000</v>
+        <v>-2127750600</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>-81</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-221421600</v>
+        <v>-222743520</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>-68</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-686817000</v>
+        <v>-690917400</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>-41</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-446387500</v>
+        <v>-449052500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>-29</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-229274000</v>
+        <v>-230642800</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 1억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 1억(0.5%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 14종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2405,11 +2405,11 @@
         <v>357</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>731778600</v>
+        <v>671017200</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.75%</t>
+          <t>0.00%→2.46%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2419,23 +2419,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-71</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-45184400</v>
+        <v>-200440100</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>7.49%→7.12%</t>
+          <t>8.45%→7.51%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>3,052→2,981</t>
+          <t>795→724</t>
         </is>
       </c>
     </row>
@@ -2449,11 +2449,11 @@
         <v>97</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>117719200</v>
+        <v>119513700</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>3.18%→3.54%</t>
+          <t>3.15%→3.52%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2463,23 +2463,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-71</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-190457500</v>
+        <v>-47338540</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>8.23%→7.29%</t>
+          <t>7.66%→7.30%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>795→724</t>
+          <t>3,052→2,981</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         <v>82</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>65413040</v>
+        <v>67536840</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2514,11 +2514,11 @@
         <v>-35</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-84304500</v>
+        <v>-93758000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>3.11%→2.71%</t>
+          <t>3.38%→2.95%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2537,7 +2537,7 @@
         <v>69</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>41154360</v>
+        <v>42430860</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2558,11 +2558,11 @@
         <v>-34</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-23524600</v>
+        <v>-23776200</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.61%→0.50%</t>
+          <t>0.60%→0.50%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2581,11 +2581,11 @@
         <v>42</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>30800280</v>
+        <v>32416440</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.42%</t>
+          <t>1.38%→1.46%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2602,11 +2602,11 @@
         <v>-31</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-25142240</v>
+        <v>-27940920</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.67%</t>
+          <t>3.08%→2.90%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2625,11 +2625,11 @@
         <v>27</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>64135800</v>
+        <v>65334600</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>2.94%→3.10%</t>
+          <t>2.92%→3.09%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2646,11 +2646,11 @@
         <v>-24</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-84626400</v>
+        <v>-87823200</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.70%</t>
+          <t>1.06%→0.71%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2669,11 +2669,11 @@
         <v>22</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>100936000</v>
+        <v>118030000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.38%</t>
+          <t>0.00%→0.43%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2690,11 +2690,11 @@
         <v>-17</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-67051400</v>
+        <v>-72083400</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.19%</t>
+          <t>0.48%→0.20%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2706,23 +2706,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>42328000</v>
+        <v>24923200</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.19%</t>
+          <t>5.73%→5.68%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>104→120</t>
+          <t>977→993</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2734,11 +2734,11 @@
         <v>-16</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-53161600</v>
+        <v>-52036800</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.31%</t>
+          <t>1.48%→1.25%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2750,23 +2750,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>24745600</v>
+        <v>41558400</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>5.83%→5.76%</t>
+          <t>1.02%→1.14%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>977→993</t>
+          <t>104→120</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -2778,11 +2778,11 @@
         <v>-3</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-34254600</v>
+        <v>-34232400</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>1.81%→1.63%</t>
+          <t>1.76%→1.59%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2801,11 +2801,11 @@
         <v>12</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>20823600</v>
+        <v>20468400</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.39%</t>
+          <t>2.28%→2.30%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2829,11 +2829,11 @@
         <v>7</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>54545400</v>
+        <v>54182800</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.23%</t>
+          <t>1.02%→1.19%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2857,11 +2857,11 @@
         <v>5</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>39775000</v>
+        <v>40774000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.19%</t>
+          <t>3.13%→3.20%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -2885,11 +2885,11 @@
         <v>5</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>22977000</v>
+        <v>23458000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.73%→2.74%</t>
+          <t>2.72%→2.74%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -2913,11 +2913,11 @@
         <v>2</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>22510800</v>
+        <v>24804800</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.08%</t>
+          <t>0.00%→0.09%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 530억   ·   현금 3억(0.6%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억   ·   현금 3억(0.6%)      오늘 2026-08-25  vs  5일전 2026-08-18      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260825.xlsx
+++ b/reports/pdf_rolling5_20260825.xlsx
@@ -1340,23 +1340,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-903413000</v>
+        <v>-196472500</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.01%</t>
+          <t>0.60%→0.48%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1368,23 +1368,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-196472500</v>
+        <v>-903413000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.48%</t>
+          <t>2.29%→2.01%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1424,23 +1424,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-451140000</v>
+        <v>-1274625000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.53%</t>
+          <t>3.45%→2.88%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>31→26</t>
+          <t>55→50</t>
         </is>
       </c>
     </row>
@@ -1452,23 +1452,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1274625000</v>
+        <v>-451140000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>3.45%→2.88%</t>
+          <t>0.66%→0.53%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>55→50</t>
+          <t>31→26</t>
         </is>
       </c>
     </row>
@@ -2706,23 +2706,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>24923200</v>
+        <v>41558400</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>5.73%→5.68%</t>
+          <t>1.02%→1.14%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>977→993</t>
+          <t>104→120</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2750,23 +2750,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>41558400</v>
+        <v>24923200</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.14%</t>
+          <t>5.73%→5.68%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>104→120</t>
+          <t>977→993</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -2850,23 +2850,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>40774000</v>
+        <v>23458000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.20%</t>
+          <t>2.72%→2.74%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>154→159</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
@@ -2878,23 +2878,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>23458000</v>
+        <v>40774000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.74%</t>
+          <t>3.13%→3.20%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>154→159</t>
+          <t>102→107</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260825.xlsx
+++ b/reports/pdf_rolling5_20260825.xlsx
@@ -1340,23 +1340,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-196472500</v>
+        <v>-903413000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.48%</t>
+          <t>2.29%→2.01%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>76→69</t>
         </is>
       </c>
     </row>
@@ -1368,23 +1368,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-903413000</v>
+        <v>-196472500</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.01%</t>
+          <t>0.60%→0.48%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>76→69</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -2419,23 +2419,23 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-71</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-200440100</v>
+        <v>-47338540</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>8.45%→7.51%</t>
+          <t>7.66%→7.30%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>795→724</t>
+          <t>3,052→2,981</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-71</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-47338540</v>
+        <v>-200440100</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>7.66%→7.30%</t>
+          <t>8.45%→7.51%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>3,052→2,981</t>
+          <t>795→724</t>
         </is>
       </c>
     </row>
@@ -2850,23 +2850,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>23458000</v>
+        <v>40774000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.74%</t>
+          <t>3.13%→3.20%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>154→159</t>
+          <t>102→107</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
@@ -2878,23 +2878,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>40774000</v>
+        <v>23458000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.20%</t>
+          <t>2.72%→2.74%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>154→159</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260825.xlsx
+++ b/reports/pdf_rolling5_20260825.xlsx
@@ -2146,23 +2146,23 @@
       <c r="E50" s="17" t="n"/>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>에임드바이오</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-892005300</v>
+        <v>-2127750600</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.40%</t>
+          <t>0.92%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>203→101</t>
+          <t>102→0</t>
         </is>
       </c>
     </row>
@@ -2174,23 +2174,23 @@
       <c r="E51" s="17" t="n"/>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>에임드바이오</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
         <v>-102</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-2127750600</v>
+        <v>-892005300</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.92%→0.00%</t>
+          <t>0.81%→0.40%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>102→0</t>
+          <t>203→101</t>
         </is>
       </c>
     </row>
@@ -2706,23 +2706,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>41558400</v>
+        <v>24923200</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.14%</t>
+          <t>5.73%→5.68%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>104→120</t>
+          <t>977→993</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2750,23 +2750,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>24923200</v>
+        <v>41558400</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>5.73%→5.68%</t>
+          <t>1.02%→1.14%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>977→993</t>
+          <t>104→120</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -2850,23 +2850,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>40774000</v>
+        <v>23458000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>3.13%→3.20%</t>
+          <t>2.72%→2.74%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>154→159</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
@@ -2878,23 +2878,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>23458000</v>
+        <v>40774000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.74%</t>
+          <t>3.13%→3.20%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>154→159</t>
+          <t>102→107</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>
